--- a/Financial Analysis/ORCL.xlsx
+++ b/Financial Analysis/ORCL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E88D691-0C45-46FB-82DD-50417AC2C1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A81A6-990A-4213-89FA-17888ACA9F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C36A60D5-C62B-4A95-9BD8-233E77289DA8}"/>
   </bookViews>
@@ -205,9 +205,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
-  </si>
-  <si>
     <t>Q126</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t>Services revenue y/y</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -290,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -313,6 +313,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -386,14 +389,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -410,7 +413,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8473440" y="15240"/>
+          <a:off x="9189720" y="15240"/>
           <a:ext cx="0" cy="9418320"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -761,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>302.49</v>
+        <v>169.01</v>
       </c>
       <c r="E3" s="10">
-        <v>45918</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="10">
-        <v>46006</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -779,10 +782,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="3">
-        <v>2841.7</v>
+        <f>2873.1</f>
+        <v>2873.1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -791,7 +795,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>859585.83299999998</v>
+        <v>485582.63099999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -799,11 +803,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>10445+560</f>
-        <v>11005</v>
+        <f>19241+525</f>
+        <v>19766</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,11 +815,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>9079+82236</f>
-        <v>91315</v>
+        <f>8091+99984</f>
+        <v>108075</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +828,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-80310</v>
+        <v>-88309</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -833,7 +837,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>939895.83299999998</v>
+        <v>573891.63099999994</v>
       </c>
     </row>
   </sheetData>
@@ -959,16 +963,16 @@
         <v>57</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="P2">
         <v>2022</v>
@@ -1031,9 +1035,9 @@
         <v>5623</v>
       </c>
       <c r="H3" s="12">
-        <v>10806</v>
-      </c>
-      <c r="I3" s="12">
+        <v>5937</v>
+      </c>
+      <c r="I3" s="14">
         <v>11007</v>
       </c>
       <c r="J3" s="12"/>
@@ -1041,16 +1045,15 @@
         <v>7186</v>
       </c>
       <c r="L3" s="12">
-        <f>K3*1.08</f>
-        <v>7760.88</v>
+        <v>7977</v>
       </c>
       <c r="M3" s="12">
         <f>L3*1.07</f>
-        <v>8304.1416000000008</v>
+        <v>8535.3900000000012</v>
       </c>
       <c r="N3" s="12">
         <f>M3*1.06</f>
-        <v>8802.390096000001</v>
+        <v>9047.5134000000016</v>
       </c>
       <c r="Q3" s="3">
         <v>35307</v>
@@ -1063,43 +1066,43 @@
       </c>
       <c r="T3" s="3">
         <f>SUM(K3:N3)</f>
-        <v>32053.411696000003</v>
+        <v>32745.903400000003</v>
       </c>
       <c r="U3" s="3">
         <f>T3*1.25</f>
-        <v>40066.764620000002</v>
+        <v>40932.379250000005</v>
       </c>
       <c r="V3" s="3">
         <f>U3*1.15</f>
-        <v>46076.779312999999</v>
+        <v>47072.236137500004</v>
       </c>
       <c r="W3" s="3">
         <f>V3*1.1</f>
-        <v>50684.4572443</v>
+        <v>51779.459751250011</v>
       </c>
       <c r="X3" s="3">
         <f>W3*1.05</f>
-        <v>53218.680106514999</v>
+        <v>54368.432738812517</v>
       </c>
       <c r="Y3" s="3">
         <f>X3*1.04</f>
-        <v>55347.427310775602</v>
+        <v>56543.17004836502</v>
       </c>
       <c r="Z3" s="3">
         <f>Y3*1.03</f>
-        <v>57007.850130098872</v>
+        <v>58239.465149815973</v>
       </c>
       <c r="AA3" s="3">
         <f t="shared" ref="AA3:AC3" si="0">Z3*1.03</f>
-        <v>58718.085634001836</v>
+        <v>59986.649104310454</v>
       </c>
       <c r="AB3" s="3">
         <f t="shared" si="0"/>
-        <v>60479.628203021894</v>
+        <v>61786.248577439772</v>
       </c>
       <c r="AC3" s="3">
         <f t="shared" si="0"/>
-        <v>62294.017049112554</v>
+        <v>63639.836034762964</v>
       </c>
     </row>
     <row r="4" spans="2:29" x14ac:dyDescent="0.3">
@@ -1120,9 +1123,9 @@
         <v>5766</v>
       </c>
       <c r="H4" s="12">
-        <v>1195</v>
-      </c>
-      <c r="I4" s="12">
+        <v>6064</v>
+      </c>
+      <c r="I4" s="14">
         <v>1129</v>
       </c>
       <c r="J4" s="12"/>
@@ -1130,16 +1133,15 @@
         <v>5721</v>
       </c>
       <c r="L4" s="12">
-        <f>K4*1.01</f>
-        <v>5778.21</v>
+        <v>5877</v>
       </c>
       <c r="M4" s="12">
         <f t="shared" ref="M4:N4" si="1">L4*1.01</f>
-        <v>5835.9921000000004</v>
+        <v>5935.77</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" si="1"/>
-        <v>5894.3520210000006</v>
+        <v>5995.1277000000009</v>
       </c>
       <c r="Q4" s="3">
         <v>5779</v>
@@ -1152,43 +1154,43 @@
       </c>
       <c r="T4" s="3">
         <f t="shared" ref="T4:T6" si="2">SUM(K4:N4)</f>
-        <v>23229.554121000001</v>
+        <v>23528.897700000001</v>
       </c>
       <c r="U4" s="3">
         <f>T4*1.02</f>
-        <v>23694.145203420001</v>
+        <v>23999.475654000002</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" ref="V4:X4" si="3">U4*1.02</f>
-        <v>24168.028107488401</v>
+        <v>24479.465167080001</v>
       </c>
       <c r="W4" s="3">
         <f t="shared" si="3"/>
-        <v>24651.388669638171</v>
+        <v>24969.054470421601</v>
       </c>
       <c r="X4" s="3">
         <f t="shared" si="3"/>
-        <v>25144.416443030936</v>
+        <v>25468.435559830032</v>
       </c>
       <c r="Y4" s="3">
         <f>X4*1.01</f>
-        <v>25395.860607461243</v>
+        <v>25723.119915428331</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" ref="Z4:AC4" si="4">Y4*1.01</f>
-        <v>25649.819213535855</v>
+        <v>25980.351114582616</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="4"/>
-        <v>25906.317405671212</v>
+        <v>26240.154625728443</v>
       </c>
       <c r="AB4" s="3">
         <f t="shared" si="4"/>
-        <v>26165.380579727924</v>
+        <v>26502.556171985729</v>
       </c>
       <c r="AC4" s="3">
         <f t="shared" si="4"/>
-        <v>26427.034385525203</v>
+        <v>26767.581733705585</v>
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.3">
@@ -1214,7 +1216,7 @@
       <c r="H5" s="12">
         <v>728</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="14">
         <v>703</v>
       </c>
       <c r="J5" s="12">
@@ -1225,8 +1227,7 @@
         <v>670</v>
       </c>
       <c r="L5" s="12">
-        <f>H5*1.01</f>
-        <v>735.28</v>
+        <v>776</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" ref="M5:N5" si="5">I5*1.01</f>
@@ -1247,43 +1248,43 @@
       </c>
       <c r="T5" s="3">
         <f t="shared" si="2"/>
-        <v>2973.81</v>
+        <v>3014.5299999999997</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" ref="U5" si="6">T5*1.02</f>
-        <v>3033.2862</v>
+        <v>3074.8206</v>
       </c>
       <c r="V5" s="3">
         <f>U5*1.01</f>
-        <v>3063.6190620000002</v>
+        <v>3105.5688060000002</v>
       </c>
       <c r="W5" s="3">
         <f t="shared" ref="W5:AC5" si="7">V5*1.01</f>
-        <v>3094.2552526200002</v>
+        <v>3136.6244940600004</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="7"/>
-        <v>3125.1978051462002</v>
+        <v>3167.9907390006006</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" si="7"/>
-        <v>3156.4497831976623</v>
+        <v>3199.6706463906066</v>
       </c>
       <c r="Z5" s="3">
         <f t="shared" si="7"/>
-        <v>3188.0142810296388</v>
+        <v>3231.667352854513</v>
       </c>
       <c r="AA5" s="3">
         <f t="shared" si="7"/>
-        <v>3219.8944238399354</v>
+        <v>3263.9840263830583</v>
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="7"/>
-        <v>3252.0933680783346</v>
+        <v>3296.6238666468889</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="7"/>
-        <v>3284.614301759118</v>
+        <v>3329.590105313358</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.3">
@@ -1309,7 +1310,7 @@
       <c r="H6" s="12">
         <v>1330</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="14">
         <v>1291</v>
       </c>
       <c r="J6" s="12">
@@ -1320,8 +1321,7 @@
         <v>1349</v>
       </c>
       <c r="L6" s="12">
-        <f>H6*1.05</f>
-        <v>1396.5</v>
+        <v>1428</v>
       </c>
       <c r="M6" s="12">
         <f>I6*1.04</f>
@@ -1342,43 +1342,43 @@
       </c>
       <c r="T6" s="3">
         <f t="shared" si="2"/>
-        <v>5477.6100000000006</v>
+        <v>5509.1100000000006</v>
       </c>
       <c r="U6" s="3">
         <f>T6*1.05</f>
-        <v>5751.4905000000008</v>
+        <v>5784.5655000000006</v>
       </c>
       <c r="V6" s="3">
         <f>U6*1.05</f>
-        <v>6039.0650250000008</v>
+        <v>6073.793775000001</v>
       </c>
       <c r="W6" s="3">
         <f>V6*1.04</f>
-        <v>6280.6276260000013</v>
+        <v>6316.7455260000015</v>
       </c>
       <c r="X6" s="3">
         <f>W6*1.03</f>
-        <v>6469.0464547800011</v>
+        <v>6506.2478917800017</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" ref="Y6:AC6" si="8">X6*1.03</f>
-        <v>6663.1178484234015</v>
+        <v>6701.4353285334018</v>
       </c>
       <c r="Z6" s="3">
         <f t="shared" si="8"/>
-        <v>6863.0113838761035</v>
+        <v>6902.4783883894042</v>
       </c>
       <c r="AA6" s="3">
         <f t="shared" si="8"/>
-        <v>7068.9017253923867</v>
+        <v>7109.5527400410865</v>
       </c>
       <c r="AB6" s="3">
         <f t="shared" si="8"/>
-        <v>7280.9687771541585</v>
+        <v>7322.8393222423192</v>
       </c>
       <c r="AC6" s="3">
         <f t="shared" si="8"/>
-        <v>7499.3978404687832</v>
+        <v>7542.5245019095892</v>
       </c>
     </row>
     <row r="7" spans="2:29" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1423,15 +1423,15 @@
       </c>
       <c r="L7" s="5">
         <f t="shared" ref="L7:N7" si="9">SUM(L3:L6)</f>
-        <v>15670.87</v>
+        <v>16058</v>
       </c>
       <c r="M7" s="5">
         <f t="shared" si="9"/>
-        <v>16192.803700000002</v>
+        <v>16523.830000000002</v>
       </c>
       <c r="N7" s="5">
         <f t="shared" si="9"/>
-        <v>16944.712117000003</v>
+        <v>17290.611100000002</v>
       </c>
       <c r="Q7" s="5">
         <f>SUM(Q3:Q6)</f>
@@ -1447,43 +1447,43 @@
       </c>
       <c r="T7" s="5">
         <f>SUM(T3:T6)</f>
-        <v>63734.385817000002</v>
+        <v>64798.441100000004</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" ref="U7:AC7" si="10">SUM(U3:U6)</f>
-        <v>72545.686523420009</v>
+        <v>73791.24100400001</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="10"/>
-        <v>79347.491507488405</v>
+        <v>80731.063885579992</v>
       </c>
       <c r="W7" s="5">
         <f t="shared" si="10"/>
-        <v>84710.728792558177</v>
+        <v>86201.884241731619</v>
       </c>
       <c r="X7" s="5">
         <f t="shared" si="10"/>
-        <v>87957.340809472153</v>
+        <v>89511.106929423142</v>
       </c>
       <c r="Y7" s="5">
         <f t="shared" si="10"/>
-        <v>90562.855549857908</v>
+        <v>92167.395938717367</v>
       </c>
       <c r="Z7" s="5">
         <f t="shared" si="10"/>
-        <v>92708.695008540468</v>
+        <v>94353.96200564249</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="10"/>
-        <v>94913.199188905375</v>
+        <v>96600.340496463032</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="10"/>
-        <v>97178.07092798232</v>
+        <v>98908.267938314704</v>
       </c>
       <c r="AC7" s="5">
         <f t="shared" si="10"/>
-        <v>99505.063576865665</v>
+        <v>101279.5323756915</v>
       </c>
     </row>
     <row r="8" spans="2:29" x14ac:dyDescent="0.3">
@@ -1520,16 +1520,15 @@
         <v>3607</v>
       </c>
       <c r="L8" s="3">
-        <f>(L3+L4)*0.29</f>
-        <v>3926.3361</v>
+        <v>3990</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" ref="M8:N8" si="13">(M3+M4)*0.29</f>
-        <v>4100.6387730000006</v>
+        <v>4196.6364000000003</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="13"/>
-        <v>4262.0552139299998</v>
+        <v>4362.3659190000008</v>
       </c>
       <c r="Q8" s="3">
         <v>7763</v>
@@ -1542,7 +1541,7 @@
       </c>
       <c r="T8" s="3">
         <f t="shared" ref="T8:T10" si="14">SUM(K8:N8)</f>
-        <v>15896.030086930001</v>
+        <v>16156.002318999999</v>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1588,8 +1587,7 @@
         <v>178</v>
       </c>
       <c r="L9" s="3">
-        <f>L5*0.28</f>
-        <v>205.8784</v>
+        <v>215</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" ref="M9:N9" si="15">M5*0.28</f>
@@ -1610,7 +1608,7 @@
       </c>
       <c r="T9" s="3">
         <f t="shared" si="14"/>
-        <v>823.06679999999994</v>
+        <v>832.1884</v>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -1656,8 +1654,7 @@
         <v>1099</v>
       </c>
       <c r="L10" s="3">
-        <f>L6*0.86</f>
-        <v>1200.99</v>
+        <v>1169</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" ref="M10:N10" si="16">M6*0.86</f>
@@ -1678,7 +1675,7 @@
       </c>
       <c r="T10" s="3">
         <f t="shared" si="14"/>
-        <v>4649.6045999999997</v>
+        <v>4617.6145999999999</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1732,15 +1729,15 @@
       </c>
       <c r="L11" s="3">
         <f t="shared" ref="L11:N11" si="18">SUM(L8:L10)</f>
-        <v>5333.2044999999998</v>
+        <v>5374</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="18"/>
-        <v>5454.1175730000004</v>
+        <v>5550.1152000000002</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="18"/>
-        <v>5697.3794139299998</v>
+        <v>5797.6901190000008</v>
       </c>
       <c r="Q11" s="3">
         <f>SUM(Q8:Q10)</f>
@@ -1756,43 +1753,43 @@
       </c>
       <c r="T11" s="3">
         <f>SUM(T8:T10)</f>
-        <v>21368.70148693</v>
+        <v>21605.805318999999</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" ref="U11:AC11" si="19">U7-U12</f>
-        <v>25390.990283197003</v>
+        <v>25826.934351399999</v>
       </c>
       <c r="V11" s="3">
         <f t="shared" si="19"/>
-        <v>26978.147112546052</v>
+        <v>27448.561721097198</v>
       </c>
       <c r="W11" s="3">
         <f t="shared" si="19"/>
-        <v>27954.540501544194</v>
+        <v>28446.621799771434</v>
       </c>
       <c r="X11" s="3">
         <f t="shared" si="19"/>
-        <v>28146.349059031083</v>
+        <v>28643.554217415403</v>
       </c>
       <c r="Y11" s="3">
         <f t="shared" si="19"/>
-        <v>28980.113775954524</v>
+        <v>29493.566700389551</v>
       </c>
       <c r="Z11" s="3">
         <f t="shared" si="19"/>
-        <v>29666.782402732948</v>
+        <v>30193.267841805595</v>
       </c>
       <c r="AA11" s="3">
         <f t="shared" si="19"/>
-        <v>30372.223740449714</v>
+        <v>30912.108958868164</v>
       </c>
       <c r="AB11" s="3">
         <f t="shared" si="19"/>
-        <v>31096.982696954336</v>
+        <v>31650.645740260705</v>
       </c>
       <c r="AC11" s="3">
         <f t="shared" si="19"/>
-        <v>31841.620344597002</v>
+        <v>32409.450360221279</v>
       </c>
     </row>
     <row r="12" spans="2:29" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1837,15 +1834,15 @@
       </c>
       <c r="L12" s="5">
         <f t="shared" ref="L12:N12" si="21">L7-L11</f>
-        <v>10337.665500000001</v>
+        <v>10684</v>
       </c>
       <c r="M12" s="5">
         <f t="shared" si="21"/>
-        <v>10738.686127000001</v>
+        <v>10973.714800000002</v>
       </c>
       <c r="N12" s="5">
         <f t="shared" si="21"/>
-        <v>11247.332703070002</v>
+        <v>11492.920981000001</v>
       </c>
       <c r="Q12" s="5">
         <f>Q7-Q11</f>
@@ -1861,43 +1858,43 @@
       </c>
       <c r="T12" s="5">
         <f>T7-T11</f>
-        <v>42365.684330069998</v>
+        <v>43192.635781000004</v>
       </c>
       <c r="U12" s="5">
         <f>U7*0.65</f>
-        <v>47154.696240223006</v>
+        <v>47964.306652600011</v>
       </c>
       <c r="V12" s="5">
         <f>V7*0.66</f>
-        <v>52369.344394942353</v>
+        <v>53282.502164482794</v>
       </c>
       <c r="W12" s="5">
         <f>W7*0.67</f>
-        <v>56756.188291013983</v>
+        <v>57755.262441960185</v>
       </c>
       <c r="X12" s="5">
         <f>X7*0.68</f>
-        <v>59810.99175044107</v>
+        <v>60867.552712007739</v>
       </c>
       <c r="Y12" s="5">
         <f t="shared" ref="Y12:AC12" si="22">Y7*0.68</f>
-        <v>61582.741773903384</v>
+        <v>62673.829238327817</v>
       </c>
       <c r="Z12" s="5">
         <f t="shared" si="22"/>
-        <v>63041.91260580752</v>
+        <v>64160.694163836895</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="22"/>
-        <v>64540.975448455662</v>
+        <v>65688.231537594867</v>
       </c>
       <c r="AB12" s="5">
         <f t="shared" si="22"/>
-        <v>66081.088231027985</v>
+        <v>67257.622198053999</v>
       </c>
       <c r="AC12" s="5">
         <f t="shared" si="22"/>
-        <v>67663.443232268663</v>
+        <v>68870.082015470223</v>
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.3">
@@ -1934,16 +1931,15 @@
         <v>2063</v>
       </c>
       <c r="L13" s="3">
-        <f>L7*0.14</f>
-        <v>2193.9218000000005</v>
+        <v>2149</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" ref="M13:N13" si="25">M7*0.14</f>
-        <v>2266.9925180000005</v>
+        <v>2313.3362000000006</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="25"/>
-        <v>2372.2596963800006</v>
+        <v>2420.6855540000006</v>
       </c>
       <c r="Q13" s="3">
         <v>8833</v>
@@ -1956,43 +1952,43 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" ref="T13:T18" si="26">SUM(K13:N13)</f>
-        <v>8896.1740143800016</v>
+        <v>8946.0217540000012</v>
       </c>
       <c r="U13" s="3">
         <f>U7*0.14</f>
-        <v>10156.396113278803</v>
+        <v>10330.773740560002</v>
       </c>
       <c r="V13" s="3">
         <f t="shared" ref="V13:AC13" si="27">V7*0.14</f>
-        <v>11108.648811048377</v>
+        <v>11302.3489439812</v>
       </c>
       <c r="W13" s="3">
         <f t="shared" si="27"/>
-        <v>11859.502030958145</v>
+        <v>12068.263793842429</v>
       </c>
       <c r="X13" s="3">
         <f t="shared" si="27"/>
-        <v>12314.027713326102</v>
+        <v>12531.554970119241</v>
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="27"/>
-        <v>12678.799776980108</v>
+        <v>12903.435431420432</v>
       </c>
       <c r="Z13" s="3">
         <f t="shared" si="27"/>
-        <v>12979.217301195667</v>
+        <v>13209.55468078995</v>
       </c>
       <c r="AA13" s="3">
         <f t="shared" si="27"/>
-        <v>13287.847886446754</v>
+        <v>13524.047669504826</v>
       </c>
       <c r="AB13" s="3">
         <f t="shared" si="27"/>
-        <v>13604.929929917525</v>
+        <v>13847.157511364059</v>
       </c>
       <c r="AC13" s="3">
         <f t="shared" si="27"/>
-        <v>13930.708900761194</v>
+        <v>14179.134532596812</v>
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.3">
@@ -2029,8 +2025,7 @@
         <v>2491</v>
       </c>
       <c r="L14" s="3">
-        <f>H14*1.1</f>
-        <v>2718.1000000000004</v>
+        <v>2561</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" ref="M14:N14" si="28">I14*1.1</f>
@@ -2051,43 +2046,43 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="26"/>
-        <v>10800.4</v>
+        <v>10643.3</v>
       </c>
       <c r="U14" s="3">
         <f>T14*1.05</f>
-        <v>11340.42</v>
+        <v>11175.465</v>
       </c>
       <c r="V14" s="3">
         <f>U14*1.04</f>
-        <v>11794.0368</v>
+        <v>11622.483600000001</v>
       </c>
       <c r="W14" s="3">
         <f>V14*1.03</f>
-        <v>12147.857904</v>
+        <v>11971.158108000001</v>
       </c>
       <c r="X14" s="3">
         <f>W14*1.02</f>
-        <v>12390.815062080001</v>
+        <v>12210.581270160003</v>
       </c>
       <c r="Y14" s="3">
         <f t="shared" ref="Y14:AC14" si="29">X14*1.01</f>
-        <v>12514.723212700801</v>
+        <v>12332.687082861603</v>
       </c>
       <c r="Z14" s="3">
         <f t="shared" si="29"/>
-        <v>12639.870444827809</v>
+        <v>12456.013953690219</v>
       </c>
       <c r="AA14" s="3">
         <f t="shared" si="29"/>
-        <v>12766.269149276088</v>
+        <v>12580.574093227122</v>
       </c>
       <c r="AB14" s="3">
         <f t="shared" si="29"/>
-        <v>12893.931840768848</v>
+        <v>12706.379834159394</v>
       </c>
       <c r="AC14" s="3">
         <f t="shared" si="29"/>
-        <v>13022.871159176537</v>
+        <v>12833.443632500988</v>
       </c>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.3">
@@ -2124,8 +2119,7 @@
         <v>376</v>
       </c>
       <c r="L15" s="3">
-        <f>H15*1.04</f>
-        <v>402.48</v>
+        <v>409</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" ref="M15:N15" si="30">I15*1.04</f>
@@ -2146,43 +2140,43 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="26"/>
-        <v>1669.76</v>
+        <v>1676.28</v>
       </c>
       <c r="U15" s="3">
         <f>T15*1.03</f>
-        <v>1719.8528000000001</v>
+        <v>1726.5684000000001</v>
       </c>
       <c r="V15" s="3">
         <f>U15*1.03</f>
-        <v>1771.4483840000003</v>
+        <v>1778.3654520000002</v>
       </c>
       <c r="W15" s="3">
         <f t="shared" ref="W15:AC15" si="31">V15*1.02</f>
-        <v>1806.8773516800004</v>
+        <v>1813.9327610400003</v>
       </c>
       <c r="X15" s="3">
         <f t="shared" si="31"/>
-        <v>1843.0148987136004</v>
+        <v>1850.2114162608004</v>
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="31"/>
-        <v>1879.8751966878724</v>
+        <v>1887.2156445860164</v>
       </c>
       <c r="Z15" s="3">
         <f t="shared" si="31"/>
-        <v>1917.4727006216299</v>
+        <v>1924.9599574777367</v>
       </c>
       <c r="AA15" s="3">
         <f t="shared" si="31"/>
-        <v>1955.8221546340626</v>
+        <v>1963.4591566272913</v>
       </c>
       <c r="AB15" s="3">
         <f t="shared" si="31"/>
-        <v>1994.9385977267439</v>
+        <v>2002.7283397598371</v>
       </c>
       <c r="AC15" s="3">
         <f t="shared" si="31"/>
-        <v>2034.8373696812787</v>
+        <v>2042.7829065550338</v>
       </c>
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.3">
@@ -2219,7 +2213,7 @@
         <v>420</v>
       </c>
       <c r="L16" s="3">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="M16" s="3">
         <v>0</v>
@@ -2238,7 +2232,7 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="26"/>
-        <v>420</v>
+        <v>827</v>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2284,7 +2278,7 @@
         <v>13</v>
       </c>
       <c r="L17" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -2303,7 +2297,7 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="26"/>
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -2349,7 +2343,7 @@
         <v>402</v>
       </c>
       <c r="L18" s="3">
-        <v>50</v>
+        <v>406</v>
       </c>
       <c r="M18" s="3">
         <v>50</v>
@@ -2368,7 +2362,7 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="26"/>
-        <v>552</v>
+        <v>908</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -2422,15 +2416,15 @@
       </c>
       <c r="L19" s="3">
         <f t="shared" ref="L19:N19" si="33">SUM(L13:L18)</f>
-        <v>5364.5018</v>
+        <v>5953</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="33"/>
-        <v>5394.4925180000009</v>
+        <v>5440.8362000000016</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="33"/>
-        <v>5827.3396963800005</v>
+        <v>5875.7655540000014</v>
       </c>
       <c r="Q19" s="3">
         <f>SUM(Q13:Q18)</f>
@@ -2446,43 +2440,43 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" ref="T19:AC19" si="34">SUM(T13:T18)</f>
-        <v>22351.334014379998</v>
+        <v>23034.601753999999</v>
       </c>
       <c r="U19" s="3">
         <f t="shared" si="34"/>
-        <v>23216.668913278801</v>
+        <v>23232.807140560002</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" si="34"/>
-        <v>24674.133995048378</v>
+        <v>24703.197995981205</v>
       </c>
       <c r="W19" s="3">
         <f t="shared" si="34"/>
-        <v>25814.237286638145</v>
+        <v>25853.35466288243</v>
       </c>
       <c r="X19" s="3">
         <f t="shared" si="34"/>
-        <v>26547.857674119707</v>
+        <v>26592.347656540045</v>
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="34"/>
-        <v>27073.398186368784</v>
+        <v>27123.33815886805</v>
       </c>
       <c r="Z19" s="3">
         <f t="shared" si="34"/>
-        <v>27536.560446645108</v>
+        <v>27590.528591957904</v>
       </c>
       <c r="AA19" s="3">
         <f t="shared" si="34"/>
-        <v>28009.939190356901</v>
+        <v>28068.080919359239</v>
       </c>
       <c r="AB19" s="3">
         <f t="shared" si="34"/>
-        <v>28493.800368413118</v>
+        <v>28556.265685283288</v>
       </c>
       <c r="AC19" s="3">
         <f t="shared" si="34"/>
-        <v>28988.41742961901</v>
+        <v>29055.361071652835</v>
       </c>
     </row>
     <row r="20" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2527,15 +2521,15 @@
       </c>
       <c r="L20" s="5">
         <f t="shared" ref="L20:N20" si="36">L12-L19</f>
-        <v>4973.163700000001</v>
+        <v>4731</v>
       </c>
       <c r="M20" s="5">
         <f t="shared" si="36"/>
-        <v>5344.1936089999999</v>
+        <v>5532.8786</v>
       </c>
       <c r="N20" s="5">
         <f t="shared" si="36"/>
-        <v>5419.9930066900015</v>
+        <v>5617.1554269999997</v>
       </c>
       <c r="Q20" s="5">
         <f>Q12-Q19</f>
@@ -2551,43 +2545,43 @@
       </c>
       <c r="T20" s="5">
         <f t="shared" ref="T20:AC20" si="37">T12-T19</f>
-        <v>20014.350315690001</v>
+        <v>20158.034027000005</v>
       </c>
       <c r="U20" s="5">
         <f t="shared" si="37"/>
-        <v>23938.027326944204</v>
+        <v>24731.499512040009</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="37"/>
-        <v>27695.210399893975</v>
+        <v>28579.304168501589</v>
       </c>
       <c r="W20" s="5">
         <f t="shared" si="37"/>
-        <v>30941.951004375838</v>
+        <v>31901.907779077756</v>
       </c>
       <c r="X20" s="5">
         <f t="shared" si="37"/>
-        <v>33263.134076321367</v>
+        <v>34275.205055467697</v>
       </c>
       <c r="Y20" s="5">
         <f t="shared" si="37"/>
-        <v>34509.343587534604</v>
+        <v>35550.491079459767</v>
       </c>
       <c r="Z20" s="5">
         <f t="shared" si="37"/>
-        <v>35505.352159162416</v>
+        <v>36570.165571878992</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="37"/>
-        <v>36531.036258098757</v>
+        <v>37620.150618235624</v>
       </c>
       <c r="AB20" s="5">
         <f t="shared" si="37"/>
-        <v>37587.287862614867</v>
+        <v>38701.356512770712</v>
       </c>
       <c r="AC20" s="5">
         <f t="shared" si="37"/>
-        <v>38675.025802649652</v>
+        <v>39814.720943817389</v>
       </c>
     </row>
     <row r="21" spans="2:150" x14ac:dyDescent="0.3">
@@ -2624,8 +2618,7 @@
         <v>923</v>
       </c>
       <c r="L21" s="3">
-        <f>H21*1.01</f>
-        <v>874.66</v>
+        <v>1057</v>
       </c>
       <c r="M21" s="3">
         <f t="shared" ref="M21:N21" si="40">I21*1.01</f>
@@ -2646,43 +2639,43 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" ref="T21:T22" si="41">SUM(K21:N21)</f>
-        <v>3686.3599999999997</v>
+        <v>3868.7</v>
       </c>
       <c r="U21" s="3">
         <f t="shared" ref="U21:AC21" si="42">T21*1.03</f>
-        <v>3796.9507999999996</v>
+        <v>3984.761</v>
       </c>
       <c r="V21" s="3">
         <f t="shared" si="42"/>
-        <v>3910.8593239999996</v>
+        <v>4104.3038299999998</v>
       </c>
       <c r="W21" s="3">
         <f t="shared" si="42"/>
-        <v>4028.1851037199995</v>
+        <v>4227.4329448999997</v>
       </c>
       <c r="X21" s="3">
         <f t="shared" si="42"/>
-        <v>4149.0306568315991</v>
+        <v>4354.255933247</v>
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="42"/>
-        <v>4273.501576536547</v>
+        <v>4484.8836112444105</v>
       </c>
       <c r="Z21" s="3">
         <f t="shared" si="42"/>
-        <v>4401.7066238326433</v>
+        <v>4619.4301195817434</v>
       </c>
       <c r="AA21" s="3">
         <f t="shared" si="42"/>
-        <v>4533.7578225476227</v>
+        <v>4758.0130231691955</v>
       </c>
       <c r="AB21" s="3">
         <f t="shared" si="42"/>
-        <v>4669.7705572240511</v>
+        <v>4900.7534138642714</v>
       </c>
       <c r="AC21" s="3">
         <f t="shared" si="42"/>
-        <v>4809.863673940773</v>
+        <v>5047.7760162801997</v>
       </c>
     </row>
     <row r="22" spans="2:150" x14ac:dyDescent="0.3">
@@ -2719,7 +2712,7 @@
         <v>-73</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>-2668</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2738,43 +2731,43 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="41"/>
-        <v>-73</v>
+        <v>-2741</v>
       </c>
       <c r="U22" s="3">
         <f t="shared" ref="U22:AC22" si="43">T22*1.02</f>
-        <v>-74.460000000000008</v>
+        <v>-2795.82</v>
       </c>
       <c r="V22" s="3">
         <f t="shared" si="43"/>
-        <v>-75.949200000000005</v>
+        <v>-2851.7364000000002</v>
       </c>
       <c r="W22" s="3">
         <f t="shared" si="43"/>
-        <v>-77.468184000000008</v>
+        <v>-2908.7711280000003</v>
       </c>
       <c r="X22" s="3">
         <f t="shared" si="43"/>
-        <v>-79.017547680000007</v>
+        <v>-2966.9465505600006</v>
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="43"/>
-        <v>-80.59789863360001</v>
+        <v>-3026.2854815712008</v>
       </c>
       <c r="Z22" s="3">
         <f t="shared" si="43"/>
-        <v>-82.209856606272012</v>
+        <v>-3086.8111912026247</v>
       </c>
       <c r="AA22" s="3">
         <f t="shared" si="43"/>
-        <v>-83.854053738397454</v>
+        <v>-3148.5474150266773</v>
       </c>
       <c r="AB22" s="3">
         <f t="shared" si="43"/>
-        <v>-85.531134813165409</v>
+        <v>-3211.5183633272109</v>
       </c>
       <c r="AC22" s="3">
         <f t="shared" si="43"/>
-        <v>-87.241757509428723</v>
+        <v>-3275.7487305937552</v>
       </c>
     </row>
     <row r="23" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2819,15 +2812,15 @@
       </c>
       <c r="L23" s="5">
         <f t="shared" ref="L23:N23" si="45">L20-L21-L22</f>
-        <v>4098.5037000000011</v>
+        <v>6342</v>
       </c>
       <c r="M23" s="5">
         <f t="shared" si="45"/>
-        <v>4443.2736089999999</v>
+        <v>4631.9585999999999</v>
       </c>
       <c r="N23" s="5">
         <f t="shared" si="45"/>
-        <v>4432.2130066900017</v>
+        <v>4629.3754269999999</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" ref="Q23:R23" si="46">Q20-Q21-Q22</f>
@@ -2843,43 +2836,43 @@
       </c>
       <c r="T23" s="5">
         <f t="shared" si="47"/>
-        <v>16400.99031569</v>
+        <v>19030.334027000004</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" si="47"/>
-        <v>20215.536526944205</v>
+        <v>23542.55851204001</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="47"/>
-        <v>23860.300275893973</v>
+        <v>27326.73673850159</v>
       </c>
       <c r="W23" s="5">
         <f t="shared" si="47"/>
-        <v>26991.23408465584</v>
+        <v>30583.245962177756</v>
       </c>
       <c r="X23" s="5">
         <f t="shared" si="47"/>
-        <v>29193.120967169765</v>
+        <v>32887.895672780694</v>
       </c>
       <c r="Y23" s="5">
         <f t="shared" si="47"/>
-        <v>30316.439909631659</v>
+        <v>34091.892949786554</v>
       </c>
       <c r="Z23" s="5">
         <f t="shared" si="47"/>
-        <v>31185.855391936042</v>
+        <v>35037.546643499874</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="47"/>
-        <v>32081.132489289528</v>
+        <v>36010.685010093104</v>
       </c>
       <c r="AB23" s="5">
         <f t="shared" si="47"/>
-        <v>33003.04844020398</v>
+        <v>37012.121462233648</v>
       </c>
       <c r="AC23" s="5">
         <f t="shared" si="47"/>
-        <v>33952.403886218308</v>
+        <v>38042.693658130942</v>
       </c>
     </row>
     <row r="24" spans="2:150" x14ac:dyDescent="0.3">
@@ -2916,16 +2909,15 @@
         <v>500</v>
       </c>
       <c r="L24" s="3">
-        <f>L23*0.12</f>
-        <v>491.82044400000012</v>
+        <v>207</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" ref="M24:N24" si="48">M23*0.12</f>
-        <v>533.19283308000001</v>
+        <v>555.83503199999996</v>
       </c>
       <c r="N24" s="3">
         <f t="shared" si="48"/>
-        <v>531.86556080280025</v>
+        <v>555.52505123999993</v>
       </c>
       <c r="Q24" s="3">
         <v>623</v>
@@ -2938,43 +2930,43 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" ref="T24" si="49">SUM(K24:N24)</f>
-        <v>2056.8788378828003</v>
+        <v>1818.3600832399998</v>
       </c>
       <c r="U24" s="3">
         <f t="shared" ref="U24:AC24" si="50">U23*0.12</f>
-        <v>2425.8643832333046</v>
+        <v>2825.1070214448009</v>
       </c>
       <c r="V24" s="3">
         <f t="shared" si="50"/>
-        <v>2863.2360331072769</v>
+        <v>3279.2084086201908</v>
       </c>
       <c r="W24" s="3">
         <f t="shared" si="50"/>
-        <v>3238.9480901587008</v>
+        <v>3669.9895154613305</v>
       </c>
       <c r="X24" s="3">
         <f t="shared" si="50"/>
-        <v>3503.1745160603718</v>
+        <v>3946.5474807336832</v>
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="50"/>
-        <v>3637.9727891557991</v>
+        <v>4091.0271539743862</v>
       </c>
       <c r="Z24" s="3">
         <f t="shared" si="50"/>
-        <v>3742.3026470323248</v>
+        <v>4204.5055972199843</v>
       </c>
       <c r="AA24" s="3">
         <f t="shared" si="50"/>
-        <v>3849.7358987147431</v>
+        <v>4321.2822012111719</v>
       </c>
       <c r="AB24" s="3">
         <f t="shared" si="50"/>
-        <v>3960.3658128244774</v>
+        <v>4441.4545754680375</v>
       </c>
       <c r="AC24" s="3">
         <f t="shared" si="50"/>
-        <v>4074.2884663461969</v>
+        <v>4565.1232389757124</v>
       </c>
     </row>
     <row r="25" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3019,15 +3011,15 @@
       </c>
       <c r="L25" s="5">
         <f t="shared" ref="L25:N25" si="52">L23-L24</f>
-        <v>3606.6832560000012</v>
+        <v>6135</v>
       </c>
       <c r="M25" s="5">
         <f t="shared" si="52"/>
-        <v>3910.0807759199997</v>
+        <v>4076.123568</v>
       </c>
       <c r="N25" s="5">
         <f t="shared" si="52"/>
-        <v>3900.3474458872015</v>
+        <v>4073.8503757600001</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" ref="Q25:R25" si="53">Q23-Q24</f>
@@ -3043,527 +3035,527 @@
       </c>
       <c r="T25" s="5">
         <f t="shared" si="54"/>
-        <v>14344.111477807201</v>
+        <v>17211.973943760004</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" si="54"/>
-        <v>17789.672143710901</v>
+        <v>20717.451490595209</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="54"/>
-        <v>20997.064242786695</v>
+        <v>24047.528329881399</v>
       </c>
       <c r="W25" s="5">
         <f t="shared" si="54"/>
-        <v>23752.285994497139</v>
+        <v>26913.256446716427</v>
       </c>
       <c r="X25" s="5">
         <f t="shared" si="54"/>
-        <v>25689.946451109394</v>
+        <v>28941.348192047011</v>
       </c>
       <c r="Y25" s="5">
         <f t="shared" si="54"/>
-        <v>26678.46712047586</v>
+        <v>30000.865795812169</v>
       </c>
       <c r="Z25" s="5">
         <f t="shared" si="54"/>
-        <v>27443.552744903718</v>
+        <v>30833.04104627989</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="54"/>
-        <v>28231.396590574786</v>
+        <v>31689.402808881932</v>
       </c>
       <c r="AB25" s="5">
         <f t="shared" si="54"/>
-        <v>29042.682627379501</v>
+        <v>32570.666886765612</v>
       </c>
       <c r="AC25" s="5">
         <f t="shared" si="54"/>
-        <v>29878.115419872112</v>
+        <v>33477.570419155229</v>
       </c>
       <c r="AD25" s="1">
         <f>AC25*(1+$AG$38)</f>
-        <v>29579.334265673391</v>
+        <v>33142.794714963675</v>
       </c>
       <c r="AE25" s="1">
         <f t="shared" ref="AE25:CP25" si="55">AD25*(1+$AG$38)</f>
-        <v>29283.540923016659</v>
+        <v>32811.366767814041</v>
       </c>
       <c r="AF25" s="1">
         <f t="shared" si="55"/>
-        <v>28990.705513786492</v>
+        <v>32483.253100135902</v>
       </c>
       <c r="AG25" s="1">
         <f t="shared" si="55"/>
-        <v>28700.798458648627</v>
+        <v>32158.420569134541</v>
       </c>
       <c r="AH25" s="1">
         <f t="shared" si="55"/>
-        <v>28413.790474062142</v>
+        <v>31836.836363443195</v>
       </c>
       <c r="AI25" s="1">
         <f t="shared" si="55"/>
-        <v>28129.652569321519</v>
+        <v>31518.467999808763</v>
       </c>
       <c r="AJ25" s="1">
         <f t="shared" si="55"/>
-        <v>27848.356043628304</v>
+        <v>31203.283319810675</v>
       </c>
       <c r="AK25" s="1">
         <f t="shared" si="55"/>
-        <v>27569.872483192023</v>
+        <v>30891.250486612567</v>
       </c>
       <c r="AL25" s="1">
         <f t="shared" si="55"/>
-        <v>27294.173758360103</v>
+        <v>30582.337981746441</v>
       </c>
       <c r="AM25" s="1">
         <f t="shared" si="55"/>
-        <v>27021.232020776501</v>
+        <v>30276.514601928975</v>
       </c>
       <c r="AN25" s="1">
         <f t="shared" si="55"/>
-        <v>26751.019700568737</v>
+        <v>29973.749455909685</v>
       </c>
       <c r="AO25" s="1">
         <f t="shared" si="55"/>
-        <v>26483.509503563047</v>
+        <v>29674.011961350589</v>
       </c>
       <c r="AP25" s="1">
         <f t="shared" si="55"/>
-        <v>26218.674408527419</v>
+        <v>29377.271841737082</v>
       </c>
       <c r="AQ25" s="1">
         <f t="shared" si="55"/>
-        <v>25956.487664442146</v>
+        <v>29083.499123319711</v>
       </c>
       <c r="AR25" s="1">
         <f t="shared" si="55"/>
-        <v>25696.922787797725</v>
+        <v>28792.664132086513</v>
       </c>
       <c r="AS25" s="1">
         <f t="shared" si="55"/>
-        <v>25439.953559919748</v>
+        <v>28504.737490765649</v>
       </c>
       <c r="AT25" s="1">
         <f t="shared" si="55"/>
-        <v>25185.554024320551</v>
+        <v>28219.690115857993</v>
       </c>
       <c r="AU25" s="1">
         <f t="shared" si="55"/>
-        <v>24933.698484077344</v>
+        <v>27937.493214699414</v>
       </c>
       <c r="AV25" s="1">
         <f t="shared" si="55"/>
-        <v>24684.361499236569</v>
+        <v>27658.118282552419</v>
       </c>
       <c r="AW25" s="1">
         <f t="shared" si="55"/>
-        <v>24437.517884244204</v>
+        <v>27381.537099726895</v>
       </c>
       <c r="AX25" s="1">
         <f t="shared" si="55"/>
-        <v>24193.142705401762</v>
+        <v>27107.721728729626</v>
       </c>
       <c r="AY25" s="1">
         <f t="shared" si="55"/>
-        <v>23951.211278347746</v>
+        <v>26836.64451144233</v>
       </c>
       <c r="AZ25" s="1">
         <f t="shared" si="55"/>
-        <v>23711.699165564267</v>
+        <v>26568.278066327905</v>
       </c>
       <c r="BA25" s="1">
         <f t="shared" si="55"/>
-        <v>23474.582173908624</v>
+        <v>26302.595285664625</v>
       </c>
       <c r="BB25" s="1">
         <f t="shared" si="55"/>
-        <v>23239.836352169539</v>
+        <v>26039.56933280798</v>
       </c>
       <c r="BC25" s="1">
         <f t="shared" si="55"/>
-        <v>23007.437988647842</v>
+        <v>25779.173639479901</v>
       </c>
       <c r="BD25" s="1">
         <f t="shared" si="55"/>
-        <v>22777.363608761363</v>
+        <v>25521.381903085101</v>
       </c>
       <c r="BE25" s="1">
         <f t="shared" si="55"/>
-        <v>22549.589972673748</v>
+        <v>25266.16808405425</v>
       </c>
       <c r="BF25" s="1">
         <f t="shared" si="55"/>
-        <v>22324.094072947009</v>
+        <v>25013.506403213709</v>
       </c>
       <c r="BG25" s="1">
         <f t="shared" si="55"/>
-        <v>22100.85313221754</v>
+        <v>24763.371339181573</v>
       </c>
       <c r="BH25" s="1">
         <f t="shared" si="55"/>
-        <v>21879.844600895365</v>
+        <v>24515.737625789756</v>
       </c>
       <c r="BI25" s="1">
         <f t="shared" si="55"/>
-        <v>21661.046154886411</v>
+        <v>24270.580249531857</v>
       </c>
       <c r="BJ25" s="1">
         <f t="shared" si="55"/>
-        <v>21444.435693337546</v>
+        <v>24027.874447036538</v>
       </c>
       <c r="BK25" s="1">
         <f t="shared" si="55"/>
-        <v>21229.991336404171</v>
+        <v>23787.595702566174</v>
       </c>
       <c r="BL25" s="1">
         <f t="shared" si="55"/>
-        <v>21017.691423040131</v>
+        <v>23549.719745540511</v>
       </c>
       <c r="BM25" s="1">
         <f t="shared" si="55"/>
-        <v>20807.514508809731</v>
+        <v>23314.222548085105</v>
       </c>
       <c r="BN25" s="1">
         <f t="shared" si="55"/>
-        <v>20599.439363721634</v>
+        <v>23081.080322604255</v>
       </c>
       <c r="BO25" s="1">
         <f t="shared" si="55"/>
-        <v>20393.444970084416</v>
+        <v>22850.269519378213</v>
       </c>
       <c r="BP25" s="1">
         <f t="shared" si="55"/>
-        <v>20189.51052038357</v>
+        <v>22621.766824184429</v>
       </c>
       <c r="BQ25" s="1">
         <f t="shared" si="55"/>
-        <v>19987.615415179735</v>
+        <v>22395.549155942586</v>
       </c>
       <c r="BR25" s="1">
         <f t="shared" si="55"/>
-        <v>19787.739261027938</v>
+        <v>22171.593664383159</v>
       </c>
       <c r="BS25" s="1">
         <f t="shared" si="55"/>
-        <v>19589.861868417658</v>
+        <v>21949.877727739327</v>
       </c>
       <c r="BT25" s="1">
         <f t="shared" si="55"/>
-        <v>19393.963249733482</v>
+        <v>21730.378950461934</v>
       </c>
       <c r="BU25" s="1">
         <f t="shared" si="55"/>
-        <v>19200.023617236147</v>
+        <v>21513.075160957316</v>
       </c>
       <c r="BV25" s="1">
         <f t="shared" si="55"/>
-        <v>19008.023381063787</v>
+        <v>21297.944409347743</v>
       </c>
       <c r="BW25" s="1">
         <f t="shared" si="55"/>
-        <v>18817.943147253151</v>
+        <v>21084.964965254265</v>
       </c>
       <c r="BX25" s="1">
         <f t="shared" si="55"/>
-        <v>18629.76371578062</v>
+        <v>20874.115315601721</v>
       </c>
       <c r="BY25" s="1">
         <f t="shared" si="55"/>
-        <v>18443.466078622812</v>
+        <v>20665.374162445703</v>
       </c>
       <c r="BZ25" s="1">
         <f t="shared" si="55"/>
-        <v>18259.031417836584</v>
+        <v>20458.720420821246</v>
       </c>
       <c r="CA25" s="1">
         <f t="shared" si="55"/>
-        <v>18076.441103658217</v>
+        <v>20254.133216613034</v>
       </c>
       <c r="CB25" s="1">
         <f t="shared" si="55"/>
-        <v>17895.676692621633</v>
+        <v>20051.591884446905</v>
       </c>
       <c r="CC25" s="1">
         <f t="shared" si="55"/>
-        <v>17716.719925695415</v>
+        <v>19851.075965602435</v>
       </c>
       <c r="CD25" s="1">
         <f t="shared" si="55"/>
-        <v>17539.552726438462</v>
+        <v>19652.565205946412</v>
       </c>
       <c r="CE25" s="1">
         <f t="shared" si="55"/>
-        <v>17364.157199174078</v>
+        <v>19456.039553886949</v>
       </c>
       <c r="CF25" s="1">
         <f t="shared" si="55"/>
-        <v>17190.515627182336</v>
+        <v>19261.47915834808</v>
       </c>
       <c r="CG25" s="1">
         <f t="shared" si="55"/>
-        <v>17018.610470910513</v>
+        <v>19068.864366764599</v>
       </c>
       <c r="CH25" s="1">
         <f t="shared" si="55"/>
-        <v>16848.424366201409</v>
+        <v>18878.175723096952</v>
       </c>
       <c r="CI25" s="1">
         <f t="shared" si="55"/>
-        <v>16679.940122539396</v>
+        <v>18689.393965865984</v>
       </c>
       <c r="CJ25" s="1">
         <f t="shared" si="55"/>
-        <v>16513.140721314001</v>
+        <v>18502.500026207323</v>
       </c>
       <c r="CK25" s="1">
         <f t="shared" si="55"/>
-        <v>16348.00931410086</v>
+        <v>18317.475025945248</v>
       </c>
       <c r="CL25" s="1">
         <f t="shared" si="55"/>
-        <v>16184.529220959852</v>
+        <v>18134.300275685797</v>
       </c>
       <c r="CM25" s="1">
         <f t="shared" si="55"/>
-        <v>16022.683928750253</v>
+        <v>17952.957272928939</v>
       </c>
       <c r="CN25" s="1">
         <f t="shared" si="55"/>
-        <v>15862.45708946275</v>
+        <v>17773.427700199649</v>
       </c>
       <c r="CO25" s="1">
         <f t="shared" si="55"/>
-        <v>15703.832518568122</v>
+        <v>17595.693423197652</v>
       </c>
       <c r="CP25" s="1">
         <f t="shared" si="55"/>
-        <v>15546.79419338244</v>
+        <v>17419.736488965675</v>
       </c>
       <c r="CQ25" s="1">
         <f t="shared" ref="CQ25:ET25" si="56">CP25*(1+$AG$38)</f>
-        <v>15391.326251448616</v>
+        <v>17245.539124076018</v>
       </c>
       <c r="CR25" s="1">
         <f t="shared" si="56"/>
-        <v>15237.412988934129</v>
+        <v>17073.083732835257</v>
       </c>
       <c r="CS25" s="1">
         <f t="shared" si="56"/>
-        <v>15085.038859044787</v>
+        <v>16902.352895506905</v>
       </c>
       <c r="CT25" s="1">
         <f t="shared" si="56"/>
-        <v>14934.188470454339</v>
+        <v>16733.329366551836</v>
       </c>
       <c r="CU25" s="1">
         <f t="shared" si="56"/>
-        <v>14784.846585749796</v>
+        <v>16565.996072886319</v>
       </c>
       <c r="CV25" s="1">
         <f t="shared" si="56"/>
-        <v>14636.998119892298</v>
+        <v>16400.336112157456</v>
       </c>
       <c r="CW25" s="1">
         <f t="shared" si="56"/>
-        <v>14490.628138693375</v>
+        <v>16236.332751035881</v>
       </c>
       <c r="CX25" s="1">
         <f t="shared" si="56"/>
-        <v>14345.721857306442</v>
+        <v>16073.969423525523</v>
       </c>
       <c r="CY25" s="1">
         <f t="shared" si="56"/>
-        <v>14202.264638733377</v>
+        <v>15913.229729290268</v>
       </c>
       <c r="CZ25" s="1">
         <f t="shared" si="56"/>
-        <v>14060.241992346044</v>
+        <v>15754.097431997365</v>
       </c>
       <c r="DA25" s="1">
         <f t="shared" si="56"/>
-        <v>13919.639572422584</v>
+        <v>15596.55645767739</v>
       </c>
       <c r="DB25" s="1">
         <f t="shared" si="56"/>
-        <v>13780.443176698358</v>
+        <v>15440.590893100616</v>
       </c>
       <c r="DC25" s="1">
         <f t="shared" si="56"/>
-        <v>13642.638744931375</v>
+        <v>15286.184984169609</v>
       </c>
       <c r="DD25" s="1">
         <f t="shared" si="56"/>
-        <v>13506.212357482062</v>
+        <v>15133.323134327913</v>
       </c>
       <c r="DE25" s="1">
         <f t="shared" si="56"/>
-        <v>13371.150233907241</v>
+        <v>14981.989902984635</v>
       </c>
       <c r="DF25" s="1">
         <f t="shared" si="56"/>
-        <v>13237.438731568169</v>
+        <v>14832.170003954789</v>
       </c>
       <c r="DG25" s="1">
         <f t="shared" si="56"/>
-        <v>13105.064344252487</v>
+        <v>14683.84830391524</v>
       </c>
       <c r="DH25" s="1">
         <f t="shared" si="56"/>
-        <v>12974.013700809963</v>
+        <v>14537.009820876086</v>
       </c>
       <c r="DI25" s="1">
         <f t="shared" si="56"/>
-        <v>12844.273563801862</v>
+        <v>14391.639722667325</v>
       </c>
       <c r="DJ25" s="1">
         <f t="shared" si="56"/>
-        <v>12715.830828163844</v>
+        <v>14247.723325440651</v>
       </c>
       <c r="DK25" s="1">
         <f t="shared" si="56"/>
-        <v>12588.672519882206</v>
+        <v>14105.246092186244</v>
       </c>
       <c r="DL25" s="1">
         <f t="shared" si="56"/>
-        <v>12462.785794683385</v>
+        <v>13964.193631264381</v>
       </c>
       <c r="DM25" s="1">
         <f t="shared" si="56"/>
-        <v>12338.15793673655</v>
+        <v>13824.551694951737</v>
       </c>
       <c r="DN25" s="1">
         <f t="shared" si="56"/>
-        <v>12214.776357369185</v>
+        <v>13686.30617800222</v>
       </c>
       <c r="DO25" s="1">
         <f t="shared" si="56"/>
-        <v>12092.628593795493</v>
+        <v>13549.443116222197</v>
       </c>
       <c r="DP25" s="1">
         <f t="shared" si="56"/>
-        <v>11971.702307857538</v>
+        <v>13413.948685059975</v>
       </c>
       <c r="DQ25" s="1">
         <f t="shared" si="56"/>
-        <v>11851.985284778963</v>
+        <v>13279.809198209376</v>
       </c>
       <c r="DR25" s="1">
         <f t="shared" si="56"/>
-        <v>11733.465431931172</v>
+        <v>13147.011106227281</v>
       </c>
       <c r="DS25" s="1">
         <f t="shared" si="56"/>
-        <v>11616.130777611861</v>
+        <v>13015.540995165007</v>
       </c>
       <c r="DT25" s="1">
         <f t="shared" si="56"/>
-        <v>11499.969469835742</v>
+        <v>12885.385585213357</v>
       </c>
       <c r="DU25" s="1">
         <f t="shared" si="56"/>
-        <v>11384.969775137384</v>
+        <v>12756.531729361222</v>
       </c>
       <c r="DV25" s="1">
         <f t="shared" si="56"/>
-        <v>11271.120077386011</v>
+        <v>12628.96641206761</v>
       </c>
       <c r="DW25" s="1">
         <f t="shared" si="56"/>
-        <v>11158.408876612151</v>
+        <v>12502.676747946933</v>
       </c>
       <c r="DX25" s="1">
         <f t="shared" si="56"/>
-        <v>11046.82478784603</v>
+        <v>12377.649980467464</v>
       </c>
       <c r="DY25" s="1">
         <f t="shared" si="56"/>
-        <v>10936.35653996757</v>
+        <v>12253.873480662789</v>
       </c>
       <c r="DZ25" s="1">
         <f t="shared" si="56"/>
-        <v>10826.992974567895</v>
+        <v>12131.33474585616</v>
       </c>
       <c r="EA25" s="1">
         <f t="shared" si="56"/>
-        <v>10718.723044822216</v>
+        <v>12010.021398397599</v>
       </c>
       <c r="EB25" s="1">
         <f t="shared" si="56"/>
-        <v>10611.535814373994</v>
+        <v>11889.921184413623</v>
       </c>
       <c r="EC25" s="1">
         <f t="shared" si="56"/>
-        <v>10505.420456230255</v>
+        <v>11771.021972569486</v>
       </c>
       <c r="ED25" s="1">
         <f t="shared" si="56"/>
-        <v>10400.366251667952</v>
+        <v>11653.311752843791</v>
       </c>
       <c r="EE25" s="1">
         <f t="shared" si="56"/>
-        <v>10296.362589151273</v>
+        <v>11536.778635315353</v>
       </c>
       <c r="EF25" s="1">
         <f t="shared" si="56"/>
-        <v>10193.39896325976</v>
+        <v>11421.410848962199</v>
       </c>
       <c r="EG25" s="1">
         <f t="shared" si="56"/>
-        <v>10091.464973627162</v>
+        <v>11307.196740472576</v>
       </c>
       <c r="EH25" s="1">
         <f t="shared" si="56"/>
-        <v>9990.5503238908914</v>
+        <v>11194.124773067851</v>
       </c>
       <c r="EI25" s="1">
         <f t="shared" si="56"/>
-        <v>9890.6448206519817</v>
+        <v>11082.183525337174</v>
       </c>
       <c r="EJ25" s="1">
         <f t="shared" si="56"/>
-        <v>9791.7383724454612</v>
+        <v>10971.361690083802</v>
       </c>
       <c r="EK25" s="1">
         <f t="shared" si="56"/>
-        <v>9693.8209887210069</v>
+        <v>10861.648073182965</v>
       </c>
       <c r="EL25" s="1">
         <f t="shared" si="56"/>
-        <v>9596.8827788337967</v>
+        <v>10753.031592451136</v>
       </c>
       <c r="EM25" s="1">
         <f t="shared" si="56"/>
-        <v>9500.9139510454588</v>
+        <v>10645.501276526624</v>
       </c>
       <c r="EN25" s="1">
         <f t="shared" si="56"/>
-        <v>9405.9048115350033</v>
+        <v>10539.046263761358</v>
       </c>
       <c r="EO25" s="1">
         <f t="shared" si="56"/>
-        <v>9311.8457634196529</v>
+        <v>10433.655801123745</v>
       </c>
       <c r="EP25" s="1">
         <f t="shared" si="56"/>
-        <v>9218.7273057854563</v>
+        <v>10329.319243112508</v>
       </c>
       <c r="EQ25" s="1">
         <f t="shared" si="56"/>
-        <v>9126.540032727602</v>
+        <v>10226.026050681383</v>
       </c>
       <c r="ER25" s="1">
         <f t="shared" si="56"/>
-        <v>9035.2746324003256</v>
+        <v>10123.76579017457</v>
       </c>
       <c r="ES25" s="1">
         <f t="shared" si="56"/>
-        <v>8944.9218860763231</v>
+        <v>10022.528132272824</v>
       </c>
       <c r="ET25" s="1">
         <f t="shared" si="56"/>
-        <v>8855.4726672155593</v>
+        <v>9922.3028509500964</v>
       </c>
     </row>
     <row r="26" spans="2:150" x14ac:dyDescent="0.3">
@@ -3600,13 +3592,16 @@
         <v>2841.7</v>
       </c>
       <c r="L26" s="3">
-        <v>2841.7</v>
+        <f>2873.1</f>
+        <v>2873.1</v>
       </c>
       <c r="M26" s="3">
-        <v>2841.7</v>
+        <f>2873.1</f>
+        <v>2873.1</v>
       </c>
       <c r="N26" s="3">
-        <v>2841.7</v>
+        <f>2873.1</f>
+        <v>2873.1</v>
       </c>
       <c r="Q26" s="3">
         <f>2797</f>
@@ -3620,34 +3615,44 @@
         <v>2841.7</v>
       </c>
       <c r="T26" s="3">
-        <v>2841.7</v>
+        <f t="shared" ref="T26:AC26" si="57">2873.1</f>
+        <v>2873.1</v>
       </c>
       <c r="U26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="V26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="W26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="X26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="Y26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="Z26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="AA26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="AB26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
       <c r="AC26" s="3">
-        <v>2841.7</v>
+        <f t="shared" si="57"/>
+        <v>2873.1</v>
       </c>
     </row>
     <row r="27" spans="2:150" x14ac:dyDescent="0.3">
@@ -3655,52 +3660,52 @@
         <v>22</v>
       </c>
       <c r="C27" s="6">
-        <f t="shared" ref="C27:K27" si="57">C25/C26</f>
+        <f t="shared" ref="C27:K27" si="58">C25/C26</f>
         <v>0.86521272792277437</v>
       </c>
       <c r="D27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.88081078227821386</v>
       </c>
       <c r="E27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.8449167751697928</v>
       </c>
       <c r="F27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.106028081782032</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0471934215230605</v>
       </c>
       <c r="H27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.1088432980258296</v>
       </c>
       <c r="I27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0331843614737657</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.2059682584368512</v>
       </c>
       <c r="K27" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0300172431994934</v>
       </c>
       <c r="L27" s="6">
-        <f t="shared" ref="L27:N27" si="58">L25/L26</f>
-        <v>1.2691991610655597</v>
+        <f t="shared" ref="L27:N27" si="59">L25/L26</f>
+        <v>2.1353242142633393</v>
       </c>
       <c r="M27" s="6">
-        <f t="shared" si="58"/>
-        <v>1.3759653643664005</v>
+        <f t="shared" si="59"/>
+        <v>1.4187196992795239</v>
       </c>
       <c r="N27" s="6">
-        <f t="shared" si="58"/>
-        <v>1.3725401857645783</v>
+        <f t="shared" si="59"/>
+        <v>1.4179285008388154</v>
       </c>
       <c r="Q27" s="6">
         <f>Q25/Q26</f>
@@ -3711,63 +3716,66 @@
         <v>3.7422238112263138</v>
       </c>
       <c r="S27" s="6">
-        <f t="shared" ref="S27:AC27" si="59">S25/S26</f>
+        <f t="shared" ref="S27:AC27" si="60">S25/S26</f>
         <v>4.3787169651968894</v>
       </c>
       <c r="T27" s="6">
-        <f t="shared" si="59"/>
-        <v>5.0477219543960308</v>
+        <f t="shared" si="60"/>
+        <v>5.9907326385298125</v>
       </c>
       <c r="U27" s="6">
-        <f t="shared" si="59"/>
-        <v>6.2602217488513574</v>
+        <f t="shared" si="60"/>
+        <v>7.2108355054106053</v>
       </c>
       <c r="V27" s="6">
-        <f t="shared" si="59"/>
-        <v>7.3889095410446899</v>
+        <f t="shared" si="60"/>
+        <v>8.3698890849192153</v>
       </c>
       <c r="W27" s="6">
-        <f t="shared" si="59"/>
-        <v>8.358477669879699</v>
+        <f t="shared" si="60"/>
+        <v>9.3673232559661788</v>
       </c>
       <c r="X27" s="6">
-        <f t="shared" si="59"/>
-        <v>9.0403443189321173</v>
+        <f t="shared" si="60"/>
+        <v>10.073212972763569</v>
       </c>
       <c r="Y27" s="6">
-        <f t="shared" si="59"/>
-        <v>9.3882067496484005</v>
+        <f t="shared" si="60"/>
+        <v>10.441984544851266</v>
       </c>
       <c r="Z27" s="6">
-        <f t="shared" si="59"/>
-        <v>9.6574419343715796</v>
+        <f t="shared" si="60"/>
+        <v>10.731628222574882</v>
       </c>
       <c r="AA27" s="6">
-        <f t="shared" si="59"/>
-        <v>9.9346857833602371</v>
+        <f t="shared" si="60"/>
+        <v>11.029690163545276</v>
       </c>
       <c r="AB27" s="6">
-        <f t="shared" si="59"/>
-        <v>10.220178987007602</v>
+        <f t="shared" si="60"/>
+        <v>11.336419507419029</v>
       </c>
       <c r="AC27" s="6">
-        <f t="shared" si="59"/>
-        <v>10.514169483010914</v>
+        <f t="shared" si="60"/>
+        <v>11.652072820004605</v>
       </c>
     </row>
     <row r="29" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K29" s="7">
-        <f t="shared" ref="K29:K32" si="60">K3/G3-1</f>
+        <f t="shared" ref="K29:L32" si="61">K3/G3-1</f>
         <v>0.27796549884403343</v>
       </c>
-      <c r="L29" s="7"/>
+      <c r="L29" s="7">
+        <f t="shared" si="61"/>
+        <v>0.34360788276907539</v>
+      </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="R29" s="7">
-        <f t="shared" ref="R29" si="61">R3/Q3-1</f>
+        <f t="shared" ref="R29" si="62">R3/Q3-1</f>
         <v>0.11544452941343075</v>
       </c>
       <c r="S29" s="7">
@@ -3776,266 +3784,269 @@
       </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7">
-        <f t="shared" ref="U29:AC29" si="62">U3/T3-1</f>
+        <f t="shared" ref="U29:AC29" si="63">U3/T3-1</f>
         <v>0.25</v>
       </c>
       <c r="V29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC29" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="30" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K30" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-7.804370447450526E-3</v>
       </c>
-      <c r="L30" s="7"/>
+      <c r="L30" s="7">
+        <f t="shared" si="61"/>
+        <v>-3.0837730870712399E-2</v>
+      </c>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="R30" s="7">
-        <f t="shared" ref="R30:AC30" si="63">R4/Q4-1</f>
+        <f t="shared" ref="R30:AC30" si="64">R4/Q4-1</f>
         <v>-0.12078214223914174</v>
       </c>
       <c r="S30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.3617398149970548E-2</v>
       </c>
       <c r="T30" s="7"/>
       <c r="U30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="V30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="W30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC30" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="31" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" ref="G31:G32" si="64">G5/C5-1</f>
+        <f t="shared" ref="G31:G32" si="65">G5/C5-1</f>
         <v>-8.2633053221288555E-2</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" ref="H31:H32" si="65">H5/D5-1</f>
+        <f t="shared" ref="H31:H32" si="66">H5/D5-1</f>
         <v>-3.703703703703709E-2</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" ref="I31:I32" si="66">I5/E5-1</f>
+        <f t="shared" ref="I31:I32" si="67">I5/E5-1</f>
         <v>-6.7639257294429656E-2</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" ref="J31:J32" si="67">J5/F5-1</f>
+        <f t="shared" ref="J31:J32" si="68">J5/F5-1</f>
         <v>9.5011876484560887E-3</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2.2900763358778553E-2</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" ref="L31:L33" si="68">L5/H5-1</f>
+        <f t="shared" ref="L31:L33" si="69">L5/H5-1</f>
+        <v>6.5934065934065922E-2</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" ref="M31:M33" si="70">M5/I5-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="M31" s="7">
-        <f t="shared" ref="M31:M33" si="69">M5/I5-1</f>
+      <c r="N31" s="7">
+        <f t="shared" ref="N31:N33" si="71">N5/J5-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="N31" s="7">
-        <f t="shared" ref="N31:N33" si="70">N5/J5-1</f>
+      <c r="R31" s="7">
+        <f t="shared" ref="R31:AC31" si="72">R5/Q5-1</f>
+        <v>-6.3530849114233345E-2</v>
+      </c>
+      <c r="S31" s="7">
+        <f t="shared" si="72"/>
+        <v>-4.24005218525767E-2</v>
+      </c>
+      <c r="T31" s="7">
+        <f t="shared" si="72"/>
+        <v>2.67472752043596E-2</v>
+      </c>
+      <c r="U31" s="7">
+        <f t="shared" si="72"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="V31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="R31" s="7">
-        <f t="shared" ref="R31:AC31" si="71">R5/Q5-1</f>
-        <v>-6.3530849114233345E-2</v>
-      </c>
-      <c r="S31" s="7">
-        <f t="shared" si="71"/>
-        <v>-4.24005218525767E-2</v>
-      </c>
-      <c r="T31" s="7">
-        <f t="shared" si="71"/>
-        <v>1.2878065395095284E-2</v>
-      </c>
-      <c r="U31" s="7">
-        <f t="shared" si="71"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="V31" s="7">
-        <f t="shared" si="71"/>
+      <c r="W31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="W31" s="7">
-        <f t="shared" si="71"/>
+      <c r="X31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="X31" s="7">
-        <f t="shared" si="71"/>
+      <c r="Y31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="Y31" s="7">
-        <f t="shared" si="71"/>
+      <c r="Z31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="Z31" s="7">
-        <f t="shared" si="71"/>
+      <c r="AA31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AA31" s="7">
-        <f t="shared" si="71"/>
+      <c r="AB31" s="7">
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AB31" s="7">
-        <f t="shared" si="71"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AC31" s="7">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="32" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-8.6767895878524959E-2</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-2.777777777777779E-2</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>-1.2241775057383331E-2</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-1.7479970866715266E-2</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.8091844813935154E-2</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
+        <v>7.3684210526315796E-2</v>
+      </c>
+      <c r="M32" s="7">
+        <f t="shared" si="70"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="N32" s="7">
+        <f t="shared" si="71"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="R32" s="7">
+        <f t="shared" ref="R32:AC32" si="73">R6/Q6-1</f>
+        <v>-2.9138362531283546E-2</v>
+      </c>
+      <c r="S32" s="7">
+        <f t="shared" si="73"/>
+        <v>-3.6457374332535486E-2</v>
+      </c>
+      <c r="T32" s="7">
+        <f t="shared" si="73"/>
+        <v>5.2763233326963643E-2</v>
+      </c>
+      <c r="U32" s="7">
+        <f t="shared" si="73"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="M32" s="7">
-        <f t="shared" si="69"/>
+      <c r="V32" s="7">
+        <f t="shared" si="73"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="W32" s="7">
+        <f t="shared" si="73"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="N32" s="7">
-        <f t="shared" si="70"/>
+      <c r="X32" s="7">
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="R32" s="7">
-        <f t="shared" ref="R32:AC32" si="72">R6/Q6-1</f>
-        <v>-2.9138362531283546E-2</v>
-      </c>
-      <c r="S32" s="7">
-        <f t="shared" si="72"/>
-        <v>-3.6457374332535486E-2</v>
-      </c>
-      <c r="T32" s="7">
-        <f t="shared" si="72"/>
-        <v>4.6743741639595049E-2</v>
-      </c>
-      <c r="U32" s="7">
-        <f t="shared" si="72"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="V32" s="7">
-        <f t="shared" si="72"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="W32" s="7">
-        <f t="shared" si="72"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="X32" s="7">
-        <f t="shared" si="72"/>
+      <c r="Y32" s="7">
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Y32" s="7">
-        <f t="shared" si="72"/>
+      <c r="Z32" s="7">
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Z32" s="7">
-        <f t="shared" si="72"/>
+      <c r="AA32" s="7">
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AA32" s="7">
-        <f t="shared" si="72"/>
+      <c r="AB32" s="7">
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AB32" s="7">
-        <f t="shared" si="72"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AC32" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -4068,64 +4079,64 @@
         <v>0.12166528894566775</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="68"/>
-        <v>0.11465040187780073</v>
+        <f t="shared" si="69"/>
+        <v>0.14218649975104913</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" si="69"/>
-        <v>0.14598752300070794</v>
+        <f t="shared" si="70"/>
+        <v>0.16941472045293704</v>
       </c>
       <c r="N33" s="8">
-        <f t="shared" si="70"/>
-        <v>6.5504126076840974E-2</v>
+        <f t="shared" si="71"/>
+        <v>8.7254675218512379E-2</v>
       </c>
       <c r="R33" s="8">
-        <f t="shared" ref="R33:AC33" si="73">R7/Q7-1</f>
+        <f t="shared" ref="R33:AC33" si="74">R7/Q7-1</f>
         <v>6.0195379749369504E-2</v>
       </c>
       <c r="S33" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8.3797511376295875E-2</v>
       </c>
       <c r="T33" s="8">
-        <f t="shared" si="73"/>
-        <v>0.11037449810972322</v>
+        <f t="shared" si="74"/>
+        <v>0.12891236955347662</v>
       </c>
       <c r="U33" s="8">
-        <f t="shared" si="73"/>
-        <v>0.13825034309924655</v>
+        <f t="shared" si="74"/>
+        <v>0.13878111496728596</v>
       </c>
       <c r="V33" s="8">
-        <f t="shared" si="73"/>
-        <v>9.3758916760303235E-2</v>
+        <f t="shared" si="74"/>
+        <v>9.4046702388482561E-2</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" si="73"/>
-        <v>6.7591768601325208E-2</v>
+        <f t="shared" si="74"/>
+        <v>6.7765988615056783E-2</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" si="73"/>
-        <v>3.8325865721972052E-2</v>
+        <f t="shared" si="74"/>
+        <v>3.838921523352834E-2</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" si="73"/>
-        <v>2.9622481948717194E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.9675524082040772E-2</v>
       </c>
       <c r="Z33" s="8">
-        <f t="shared" si="73"/>
-        <v>2.3694476567174938E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.3723856409906485E-2</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" si="73"/>
-        <v>2.3778828729730472E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.380799325296179E-2</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" si="73"/>
-        <v>2.3862558194558181E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.3891504211997816E-2</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" si="73"/>
-        <v>2.3945655914572095E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.3974380370867188E-2</v>
       </c>
     </row>
     <row r="34" spans="2:33" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4133,28 +4144,28 @@
         <v>49</v>
       </c>
       <c r="C34" s="7">
-        <f t="shared" ref="C34:E34" si="74">((C3+C4)-C8)/(C3+C4)</f>
+        <f t="shared" ref="C34:E34" si="75">((C3+C4)-C8)/(C3+C4)</f>
         <v>0.78959057551178058</v>
       </c>
       <c r="D34" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.78977535361005824</v>
       </c>
       <c r="E34" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.78144219627417777</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7">
-        <f t="shared" ref="G34:I34" si="75">((G3+G4)-G8)/(G3+G4)</f>
+        <f t="shared" ref="G34:I34" si="76">((G3+G4)-G8)/(G3+G4)</f>
         <v>0.7719729563614014</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.77118573452212313</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.76252471984179304</v>
       </c>
       <c r="J34" s="7"/>
@@ -4163,32 +4174,32 @@
         <v>0.72053924227163557</v>
       </c>
       <c r="L34" s="7">
-        <f t="shared" ref="L34:N34" si="76">((L3+L4)-L8)/(L3+L4)</f>
+        <f t="shared" ref="L34:N34" si="77">((L3+L4)-L8)/(L3+L4)</f>
+        <v>0.71199653529666518</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="77"/>
         <v>0.71</v>
       </c>
-      <c r="M34" s="7">
-        <f t="shared" si="76"/>
+      <c r="N34" s="7">
+        <f t="shared" si="77"/>
         <v>0.71</v>
       </c>
-      <c r="N34" s="7">
-        <f t="shared" si="76"/>
-        <v>0.71000000000000008</v>
-      </c>
       <c r="Q34" s="7">
-        <f t="shared" ref="Q34:T34" si="77">((Q3+Q4)-Q8)/(Q3+Q4)</f>
+        <f t="shared" ref="Q34:T34" si="78">((Q3+Q4)-Q8)/(Q3+Q4)</f>
         <v>0.81105486053643572</v>
       </c>
       <c r="R34" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.78798578625404825</v>
       </c>
       <c r="S34" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.76500101564086942</v>
       </c>
       <c r="T34" s="7">
-        <f t="shared" si="77"/>
-        <v>0.71246061328276589</v>
+        <f t="shared" si="78"/>
+        <v>0.71290876194673924</v>
       </c>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
@@ -4205,35 +4216,35 @@
         <v>46</v>
       </c>
       <c r="C35" s="7">
-        <f t="shared" ref="C35:F35" si="78">(C5-C9)/C5</f>
+        <f t="shared" ref="C35:F35" si="79">(C5-C9)/C5</f>
         <v>0.69327731092436973</v>
       </c>
       <c r="D35" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.71825396825396826</v>
       </c>
       <c r="E35" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.71220159151193629</v>
       </c>
       <c r="F35" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.71258907363420432</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" ref="G35:J35" si="79">(G5-G9)/G5</f>
+        <f t="shared" ref="G35:J35" si="80">(G5-G9)/G5</f>
         <v>0.75267175572519085</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.76373626373626369</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.7197724039829303</v>
       </c>
       <c r="J35" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.70470588235294118</v>
       </c>
       <c r="K35" s="7">
@@ -4241,32 +4252,32 @@
         <v>0.73432835820895526</v>
       </c>
       <c r="L35" s="7">
-        <f t="shared" ref="L35:N35" si="80">(L5-L9)/L5</f>
-        <v>0.71999999999999986</v>
+        <f t="shared" ref="L35:N35" si="81">(L5-L9)/L5</f>
+        <v>0.72293814432989689</v>
       </c>
       <c r="M35" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.72</v>
       </c>
       <c r="N35" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.72</v>
       </c>
       <c r="Q35" s="7">
-        <f t="shared" ref="Q35:T35" si="81">(Q5-Q9)/Q5</f>
+        <f t="shared" ref="Q35:T35" si="82">(Q5-Q9)/Q5</f>
         <v>0.68234575442883327</v>
       </c>
       <c r="R35" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.70939334637964779</v>
       </c>
       <c r="S35" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.73365122615803813</v>
       </c>
       <c r="T35" s="7">
-        <f t="shared" si="81"/>
-        <v>0.7232281820291141</v>
+        <f t="shared" si="82"/>
+        <v>0.72394091284545181</v>
       </c>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -4283,35 +4294,35 @@
         <v>47</v>
       </c>
       <c r="C36" s="7">
-        <f t="shared" ref="C36:F36" si="82">(C6-C10)/C6</f>
+        <f t="shared" ref="C36:F36" si="83">(C6-C10)/C6</f>
         <v>0.12364425162689804</v>
       </c>
       <c r="D36" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>8.4064327485380119E-2</v>
       </c>
       <c r="E36" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>8.1866870696250954E-2</v>
       </c>
       <c r="F36" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.1551347414420976</v>
       </c>
       <c r="G36" s="7">
-        <f t="shared" ref="G36:J36" si="83">(G6-G10)/G6</f>
+        <f t="shared" ref="G36:J36" si="84">(G6-G10)/G6</f>
         <v>9.1844813935075223E-2</v>
       </c>
       <c r="H36" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0.12255639097744361</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0.13555383423702555</v>
       </c>
       <c r="J36" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0.15048183839881393</v>
       </c>
       <c r="K36" s="7">
@@ -4319,32 +4330,32 @@
         <v>0.18532246108228317</v>
       </c>
       <c r="L36" s="7">
-        <f t="shared" ref="L36:N36" si="84">(L6-L10)/L6</f>
-        <v>0.13999999999999999</v>
+        <f t="shared" ref="L36:N36" si="85">(L6-L10)/L6</f>
+        <v>0.18137254901960784</v>
       </c>
       <c r="M36" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.1400000000000001</v>
       </c>
       <c r="N36" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.14000000000000007</v>
       </c>
       <c r="Q36" s="7">
-        <f t="shared" ref="Q36:T36" si="85">(Q6-Q10)/Q6</f>
+        <f t="shared" ref="Q36:T36" si="86">(Q6-Q10)/Q6</f>
         <v>0.14890954594208081</v>
       </c>
       <c r="R36" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.11158166083594181</v>
       </c>
       <c r="S36" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.12554939805083126</v>
       </c>
       <c r="T36" s="7">
-        <f t="shared" si="85"/>
-        <v>0.1511618023188947</v>
+        <f t="shared" si="86"/>
+        <v>0.16182203659030236</v>
       </c>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
@@ -4361,104 +4372,104 @@
         <v>24</v>
       </c>
       <c r="C37" s="8">
-        <f t="shared" ref="C37:K37" si="86">C12/C7</f>
+        <f t="shared" ref="C37:K37" si="87">C12/C7</f>
         <v>0.71011001365132898</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.71099605903716867</v>
       </c>
       <c r="E37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.70865963855421688</v>
       </c>
       <c r="F37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.72534471897529218</v>
       </c>
       <c r="G37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.70647027880063129</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.70943879365530982</v>
       </c>
       <c r="I37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.70311394196744514</v>
       </c>
       <c r="J37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.70188014839967305</v>
       </c>
       <c r="K37" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.67278574299879401</v>
       </c>
       <c r="L37" s="8">
-        <f t="shared" ref="L37:N37" si="87">L12/L7</f>
-        <v>0.65967400023100187</v>
+        <f t="shared" ref="L37:N37" si="88">L12/L7</f>
+        <v>0.66533814920911694</v>
       </c>
       <c r="M37" s="8">
-        <f t="shared" si="87"/>
-        <v>0.66317645331549346</v>
+        <f t="shared" si="88"/>
+        <v>0.66411448193306277</v>
       </c>
       <c r="N37" s="8">
-        <f t="shared" si="87"/>
-        <v>0.66376652641893918</v>
+        <f t="shared" si="88"/>
+        <v>0.66469142788134306</v>
       </c>
       <c r="Q37" s="8">
-        <f t="shared" ref="Q37:AC37" si="88">Q12/Q7</f>
+        <f t="shared" ref="Q37:AC37" si="89">Q12/Q7</f>
         <v>0.72847019257717105</v>
       </c>
       <c r="R37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.71407261947470779</v>
       </c>
       <c r="S37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.70509939197547</v>
       </c>
       <c r="T37" s="8">
-        <f t="shared" si="88"/>
-        <v>0.66472256360505655</v>
+        <f t="shared" si="89"/>
+        <v>0.66656905702936742</v>
       </c>
       <c r="U37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.65</v>
       </c>
       <c r="V37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.66</v>
       </c>
       <c r="W37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.67</v>
       </c>
       <c r="X37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.68</v>
       </c>
       <c r="Y37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.68</v>
       </c>
       <c r="Z37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.68</v>
       </c>
       <c r="AA37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.68</v>
       </c>
       <c r="AB37" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.68</v>
       </c>
       <c r="AC37" s="8">
-        <f t="shared" si="88"/>
-        <v>0.68000000000000016</v>
+        <f t="shared" si="89"/>
+        <v>0.68</v>
       </c>
     </row>
     <row r="38" spans="2:33" x14ac:dyDescent="0.3">
@@ -4466,103 +4477,103 @@
         <v>25</v>
       </c>
       <c r="C38" s="7">
-        <f t="shared" ref="C38:K38" si="89">C13/C7</f>
+        <f t="shared" ref="C38:K38" si="90">C13/C7</f>
         <v>0.16269172087047298</v>
       </c>
       <c r="D38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.16173402364577699</v>
       </c>
       <c r="E38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.15376506024096387</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.14789668929796318</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.15300217930412566</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.15577210327903834</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.1499646142958245</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.14500408727912972</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.13821519496181162</v>
       </c>
       <c r="L38" s="7">
-        <f t="shared" ref="L38:N38" si="90">L13/L7</f>
-        <v>0.14000000000000001</v>
+        <f t="shared" ref="L38:N38" si="91">L13/L7</f>
+        <v>0.13382737576285963</v>
       </c>
       <c r="M38" s="7">
-        <f t="shared" si="90"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="N38" s="7">
-        <f t="shared" si="90"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q38" s="7">
-        <f t="shared" ref="Q38:AC38" si="91">Q13/Q7</f>
-        <v>0.17682267686271369</v>
-      </c>
-      <c r="R38" s="7">
-        <f t="shared" si="91"/>
-        <v>0.15622816789713184</v>
-      </c>
-      <c r="S38" s="7">
-        <f t="shared" si="91"/>
-        <v>0.15071691144445026</v>
-      </c>
-      <c r="T38" s="7">
-        <f t="shared" si="91"/>
-        <v>0.13958201527074426</v>
-      </c>
-      <c r="U38" s="7">
         <f t="shared" si="91"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="V38" s="7">
+      <c r="N38" s="7">
         <f t="shared" si="91"/>
         <v>0.14000000000000001</v>
       </c>
+      <c r="Q38" s="7">
+        <f t="shared" ref="Q38:AC38" si="92">Q13/Q7</f>
+        <v>0.17682267686271369</v>
+      </c>
+      <c r="R38" s="7">
+        <f t="shared" si="92"/>
+        <v>0.15622816789713184</v>
+      </c>
+      <c r="S38" s="7">
+        <f t="shared" si="92"/>
+        <v>0.15071691144445026</v>
+      </c>
+      <c r="T38" s="7">
+        <f t="shared" si="92"/>
+        <v>0.13805921256954437</v>
+      </c>
+      <c r="U38" s="7">
+        <f t="shared" si="92"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V38" s="7">
+        <f t="shared" si="92"/>
+        <v>0.14000000000000001</v>
+      </c>
       <c r="W38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="X38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Y38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Z38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AA38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AB38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AC38" s="7">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AF38" t="s">
@@ -4581,35 +4592,35 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7">
-        <f t="shared" ref="G39:K40" si="92">G14/C14-1</f>
+        <f t="shared" ref="G39:K40" si="93">G14/C14-1</f>
         <v>4.0613718411552258E-2</v>
       </c>
       <c r="H39" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.11006289308176109</v>
       </c>
       <c r="I39" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>8.0516014234875533E-2</v>
       </c>
       <c r="J39" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.19280898876404495</v>
       </c>
       <c r="K39" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>8.0225498699046049E-2</v>
       </c>
       <c r="L39" s="7">
-        <f t="shared" ref="L39:N39" si="93">L14/H14-1</f>
+        <f t="shared" ref="L39:N39" si="94">L14/H14-1</f>
+        <v>3.6422501011736053E-2</v>
+      </c>
+      <c r="M39" s="7">
+        <f t="shared" si="94"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="M39" s="7">
-        <f t="shared" si="93"/>
-        <v>0.10000000000000009</v>
-      </c>
       <c r="N39" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="Q39" s="7"/>
@@ -4618,54 +4629,54 @@
         <v>3.3862924736170807E-2</v>
       </c>
       <c r="S39" s="7">
-        <f t="shared" ref="S39:AC39" si="94">S14/R14-1</f>
+        <f t="shared" ref="S39:AC39" si="95">S14/R14-1</f>
         <v>0.10600112170499165</v>
       </c>
       <c r="T39" s="7">
-        <f t="shared" si="94"/>
-        <v>9.5375253549695671E-2</v>
+        <f t="shared" si="95"/>
+        <v>7.9442190669371193E-2</v>
       </c>
       <c r="U39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="V39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="W39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="X39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="Z39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AA39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AB39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AC39" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF39" t="s">
         <v>31</v>
       </c>
       <c r="AG39" s="7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="40" spans="2:33" x14ac:dyDescent="0.3">
@@ -4677,35 +4688,35 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>-8.9058524173027953E-2</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3.2000000000000028E-2</v>
       </c>
       <c r="I40" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3.4482758620689724E-2</v>
       </c>
       <c r="J40" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0.15880893300248133</v>
       </c>
       <c r="K40" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5.027932960893855E-2</v>
       </c>
       <c r="L40" s="7">
-        <f t="shared" ref="L40:N40" si="95">L15/H15-1</f>
+        <f t="shared" ref="L40:N40" si="96">L15/H15-1</f>
+        <v>5.6847545219638196E-2</v>
+      </c>
+      <c r="M40" s="7">
+        <f t="shared" si="96"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="M40" s="7">
-        <f t="shared" si="95"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
       <c r="N40" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="Q40" s="7"/>
@@ -4714,55 +4725,55 @@
         <v>-1.9632678910702972E-2</v>
       </c>
       <c r="S40" s="7">
-        <f t="shared" ref="S40:AC40" si="96">S15/R15-1</f>
+        <f t="shared" ref="S40:AC40" si="97">S15/R15-1</f>
         <v>3.488372093023262E-2</v>
       </c>
       <c r="T40" s="7">
-        <f t="shared" si="96"/>
-        <v>4.2297128589263489E-2</v>
+        <f t="shared" si="97"/>
+        <v>4.6367041198501768E-2</v>
       </c>
       <c r="U40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="V40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="W40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Y40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="Z40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC40" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF40" t="s">
         <v>32</v>
       </c>
       <c r="AG40" s="3">
-        <f>NPV(AG39,S25:ET25)</f>
-        <v>474322.49503531365</v>
+        <f>NPV(AG39,T25:ET25)</f>
+        <v>461635.53014038643</v>
       </c>
     </row>
     <row r="41" spans="2:33" x14ac:dyDescent="0.3">
@@ -4770,111 +4781,111 @@
         <v>28</v>
       </c>
       <c r="C41" s="7">
-        <f t="shared" ref="C41:K41" si="97">C20/C7</f>
+        <f t="shared" ref="C41:K41" si="98">C20/C7</f>
         <v>0.26467517867180601</v>
       </c>
       <c r="D41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.27988563480411094</v>
       </c>
       <c r="E41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.28237951807228917</v>
       </c>
       <c r="F41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.32792048715615596</v>
       </c>
       <c r="G41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.2999173367400616</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.30016359627285011</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.30842179759377214</v>
       </c>
       <c r="J41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.32126013959630256</v>
       </c>
       <c r="K41" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.28654696502746885</v>
       </c>
       <c r="L41" s="7">
-        <f t="shared" ref="L41:N41" si="98">L20/L7</f>
-        <v>0.31735083629689997</v>
+        <f t="shared" ref="L41:N41" si="99">L20/L7</f>
+        <v>0.29461950429692363</v>
       </c>
       <c r="M41" s="7">
-        <f t="shared" si="98"/>
-        <v>0.33003510127156049</v>
+        <f t="shared" si="99"/>
+        <v>0.33484238218379148</v>
       </c>
       <c r="N41" s="7">
-        <f t="shared" si="98"/>
-        <v>0.31986338683513676</v>
+        <f t="shared" si="99"/>
+        <v>0.32486737423641432</v>
       </c>
       <c r="Q41" s="7">
-        <f t="shared" ref="Q41:AC41" si="99">Q20/Q7</f>
+        <f t="shared" ref="Q41:AC41" si="100">Q20/Q7</f>
         <v>0.26210113304239901</v>
       </c>
       <c r="R41" s="7">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.28989256245161532</v>
       </c>
       <c r="S41" s="7">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.30798445965957594</v>
       </c>
       <c r="T41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.31402750742993013</v>
+        <f t="shared" si="100"/>
+        <v>0.311088255902502</v>
       </c>
       <c r="U41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.32997175261710787</v>
+        <f t="shared" si="100"/>
+        <v>0.33515494760007336</v>
       </c>
       <c r="V41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.34903700008311217</v>
+        <f t="shared" si="100"/>
+        <v>0.35400628696045666</v>
       </c>
       <c r="W41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.36526602291602622</v>
+        <f t="shared" si="100"/>
+        <v>0.37008364793531467</v>
       </c>
       <c r="X41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.37817348467109696</v>
+        <f t="shared" si="100"/>
+        <v>0.38291566523127329</v>
       </c>
       <c r="Y41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.38105405773712653</v>
+        <f t="shared" si="100"/>
+        <v>0.38571656188591347</v>
       </c>
       <c r="Z41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.3829775853914415</v>
+        <f t="shared" si="100"/>
+        <v>0.38758484322780262</v>
       </c>
       <c r="AA41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.38488889396079862</v>
+        <f t="shared" si="100"/>
+        <v>0.3894411802783766</v>
       </c>
       <c r="AB41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.38678775472370125</v>
+        <f t="shared" si="100"/>
+        <v>0.39128535277664822</v>
       </c>
       <c r="AC41" s="7">
-        <f t="shared" si="99"/>
-        <v>0.38867394695722163</v>
+        <f t="shared" si="100"/>
+        <v>0.3931171482518957</v>
       </c>
       <c r="AF41" t="s">
         <v>33</v>
       </c>
       <c r="AG41" s="3">
         <f>Main!D8</f>
-        <v>-80310</v>
+        <v>-88309</v>
       </c>
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.3">
@@ -4882,52 +4893,52 @@
         <v>20</v>
       </c>
       <c r="C42" s="7">
-        <f t="shared" ref="C42:K42" si="100">C24/C23</f>
+        <f t="shared" ref="C42:K42" si="101">C24/C23</f>
         <v>-1.8947368421052633E-2</v>
       </c>
       <c r="D42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>7.9779411764705876E-2</v>
       </c>
       <c r="E42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.16195462478184991</v>
       </c>
       <c r="F42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.16873842898704047</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>7.5733669927421893E-2</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>7.0501474926253693E-2</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.14849187935034802</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.17481338791235251</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.14590020426028597</v>
       </c>
       <c r="L42" s="7">
-        <f t="shared" ref="L42:N42" si="101">L24/L23</f>
+        <f t="shared" ref="L42:N42" si="102">L24/L23</f>
+        <v>3.2639545884578999E-2</v>
+      </c>
+      <c r="M42" s="7">
+        <f t="shared" si="102"/>
         <v>0.12</v>
       </c>
-      <c r="M42" s="7">
-        <f t="shared" si="101"/>
-        <v>0.12000000000000001</v>
-      </c>
       <c r="N42" s="7">
-        <f t="shared" si="101"/>
-        <v>0.12000000000000001</v>
+        <f t="shared" si="102"/>
+        <v>0.11999999999999998</v>
       </c>
       <c r="Q42" s="7">
         <f>Q24/Q23</f>
@@ -4938,55 +4949,55 @@
         <v>0.10850864491951281</v>
       </c>
       <c r="S42" s="7">
-        <f t="shared" ref="S42:AC42" si="102">S24/S23</f>
+        <f t="shared" ref="S42:AC42" si="103">S24/S23</f>
         <v>0.12125706214689265</v>
       </c>
       <c r="T42" s="7">
-        <f t="shared" si="102"/>
-        <v>0.12541186832572471</v>
+        <f t="shared" si="103"/>
+        <v>9.5550613071748128E-2</v>
       </c>
       <c r="U42" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="V42" s="7">
+        <f t="shared" si="103"/>
         <v>0.12</v>
       </c>
-      <c r="V42" s="7">
-        <f t="shared" si="102"/>
-        <v>0.12000000000000001</v>
-      </c>
       <c r="W42" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.12</v>
       </c>
       <c r="X42" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.12</v>
       </c>
       <c r="Y42" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.12</v>
       </c>
       <c r="Z42" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AA42" s="7">
+        <f t="shared" si="103"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AB42" s="7">
+        <f t="shared" si="103"/>
         <v>0.12</v>
       </c>
-      <c r="AA42" s="7">
-        <f t="shared" si="102"/>
-        <v>0.12</v>
-      </c>
-      <c r="AB42" s="7">
-        <f t="shared" si="102"/>
-        <v>0.12</v>
-      </c>
       <c r="AC42" s="7">
-        <f t="shared" si="102"/>
-        <v>0.12</v>
+        <f t="shared" si="103"/>
+        <v>0.11999999999999998</v>
       </c>
       <c r="AF42" t="s">
         <v>34</v>
       </c>
       <c r="AG42" s="3">
         <f>AG40+AG41</f>
-        <v>394012.49503531365</v>
+        <v>373326.53014038643</v>
       </c>
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.3">
@@ -4994,111 +5005,111 @@
         <v>29</v>
       </c>
       <c r="C43" s="7">
-        <f t="shared" ref="C43:K43" si="103">C25/C7</f>
+        <f t="shared" ref="C43:K43" si="104">C25/C7</f>
         <v>0.19433068336946921</v>
       </c>
       <c r="D43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.19341627385827989</v>
       </c>
       <c r="E43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.18079819277108433</v>
       </c>
       <c r="F43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.21999020088192062</v>
       </c>
       <c r="G43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.22010971669046367</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.22412689380468029</v>
       </c>
       <c r="I43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.20778485491861287</v>
       </c>
       <c r="J43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.21549393196252278</v>
       </c>
       <c r="K43" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.19610076376792174</v>
       </c>
       <c r="L43" s="7">
-        <f t="shared" ref="L43:N43" si="104">L25/L7</f>
-        <v>0.23015207553888209</v>
+        <f t="shared" ref="L43:N43" si="105">L25/L7</f>
+        <v>0.3820525594719143</v>
       </c>
       <c r="M43" s="7">
-        <f t="shared" si="104"/>
-        <v>0.24147027583123232</v>
+        <f t="shared" si="105"/>
+        <v>0.24668152407765026</v>
       </c>
       <c r="N43" s="7">
-        <f t="shared" si="104"/>
-        <v>0.23018080324741116</v>
+        <f t="shared" si="105"/>
+        <v>0.23561054911240237</v>
       </c>
       <c r="Q43" s="7">
-        <f t="shared" ref="Q43:AC43" si="105">Q25/Q7</f>
+        <f t="shared" ref="Q43:AC43" si="106">Q25/Q7</f>
         <v>0.17021659927132962</v>
       </c>
       <c r="R43" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.19763599629916354</v>
       </c>
       <c r="S43" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.21678078015296434</v>
       </c>
       <c r="T43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.22506079401146697</v>
+        <f t="shared" si="106"/>
+        <v>0.26562327197343644</v>
       </c>
       <c r="U43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.24522026044881165</v>
+        <f t="shared" si="106"/>
+        <v>0.28075759681927798</v>
       </c>
       <c r="V43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.26462165147092398</v>
+        <f t="shared" si="106"/>
+        <v>0.2978720603009013</v>
       </c>
       <c r="W43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.28039288922495698</v>
+        <f t="shared" si="106"/>
+        <v>0.31221192765630196</v>
       </c>
       <c r="X43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.29207279591088814</v>
+        <f t="shared" si="106"/>
+        <v>0.32332689411232962</v>
       </c>
       <c r="Y43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.29458509185135467</v>
+        <f t="shared" si="106"/>
+        <v>0.32550410576599037</v>
       </c>
       <c r="Z43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.29601918937997751</v>
+        <f t="shared" si="106"/>
+        <v>0.32678056534007582</v>
       </c>
       <c r="AA43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.29744436845275807</v>
+        <f t="shared" si="106"/>
+        <v>0.32804649182413825</v>
       </c>
       <c r="AB43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.2988604563770641</v>
+        <f t="shared" si="106"/>
+        <v>0.32930176178071069</v>
       </c>
       <c r="AC43" s="7">
-        <f t="shared" si="105"/>
-        <v>0.30026728636570205</v>
+        <f t="shared" si="106"/>
+        <v>0.33054625780628416</v>
       </c>
       <c r="AF43" t="s">
         <v>35</v>
       </c>
       <c r="AG43" s="2">
         <f>AG42/AC26</f>
-        <v>138.65379703533577</v>
+        <v>129.93857858772282</v>
       </c>
     </row>
     <row r="44" spans="2:33" x14ac:dyDescent="0.3">
@@ -5107,7 +5118,7 @@
       </c>
       <c r="AG44" s="2">
         <f>Main!D3</f>
-        <v>302.49</v>
+        <v>169.01</v>
       </c>
     </row>
     <row r="45" spans="2:33" x14ac:dyDescent="0.3">
@@ -5116,7 +5127,7 @@
       </c>
       <c r="AG45" s="8">
         <f>AG43/AG44-1</f>
-        <v>-0.5416251874926914</v>
+        <v>-0.23117816349492437</v>
       </c>
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.3">
@@ -5124,7 +5135,7 @@
         <v>58</v>
       </c>
       <c r="AG46" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
